--- a/Digitised_Records_High_Frequency_2026_05_06.xlsx
+++ b/Digitised_Records_High_Frequency_2026_05_06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sotonac-my.sharepoint.com/personal/ck1g20_soton_ac_uk/Documents/Documents/PhD/20_Historical_record_catalogue/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{20516951-3379-4B2C-8F4C-42D953C85CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DFDAA41-BAF9-45F9-8D78-390149F7AE1D}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{20516951-3379-4B2C-8F4C-42D953C85CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EA14678-FA2F-458E-B334-EB6B8AC3D38F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8FB86131-9B33-41BE-BB40-45738662AB11}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="503">
   <si>
     <t>Study</t>
   </si>
@@ -458,9 +458,6 @@
     <t>1893-1913, 1943-1955</t>
   </si>
   <si>
-    <t>Custom made software</t>
-  </si>
-  <si>
     <t>https://www.sciencedirect.com/science/article/pii/S002216941201092X#s0010</t>
   </si>
   <si>
@@ -1344,9 +1341,6 @@
   </si>
   <si>
     <t>Wöpplemann et al., 2006</t>
-  </si>
-  <si>
-    <t>Undefined</t>
   </si>
   <si>
     <r>
@@ -1409,18 +1403,12 @@
     <t>1873, 1880-1884</t>
   </si>
   <si>
-    <t>Line detecting software</t>
-  </si>
-  <si>
     <t>1874-1875, 1886-1887</t>
   </si>
   <si>
     <t xml:space="preserve">Marigrams </t>
   </si>
   <si>
-    <t>UnGraph (Digitisation software)</t>
-  </si>
-  <si>
     <t>Marigrams and Digital</t>
   </si>
   <si>
@@ -1490,9 +1478,6 @@
     <t>1865-1886, 1888-1889, various months missing in the record</t>
   </si>
   <si>
-    <t>Line finding algorithims</t>
-  </si>
-  <si>
     <t>1868-1870</t>
   </si>
   <si>
@@ -1526,9 +1511,6 @@
     <t>1939-1978</t>
   </si>
   <si>
-    <t>Specalised Algorthim</t>
-  </si>
-  <si>
     <t>1936-1952</t>
   </si>
   <si>
@@ -1581,6 +1563,12 @@
   </si>
   <si>
     <t>Hogarth et al., In review</t>
+  </si>
+  <si>
+    <t>Specalised Algorithm</t>
+  </si>
+  <si>
+    <t>UnGraph</t>
   </si>
 </sst>
 </file>
@@ -1812,6 +1800,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2143,9 +2135,9 @@
     <col min="8" max="8" width="20.81640625" style="5" customWidth="1"/>
     <col min="9" max="9" width="31.1796875" style="3" customWidth="1"/>
     <col min="10" max="10" width="13.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="36.6328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="32.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.1796875" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="157.1796875" style="3" bestFit="1" customWidth="1"/>
     <col min="23" max="16384" width="8.7265625" style="3"/>
   </cols>
@@ -2173,13 +2165,13 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>8</v>
@@ -2188,7 +2180,7 @@
         <v>9</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>11</v>
@@ -2196,7 +2188,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>13</v>
@@ -2228,7 +2220,7 @@
         <v>136.16666666666666</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>10</v>
@@ -2242,7 +2234,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>18</v>
@@ -2274,7 +2266,7 @@
         <v>137.13636363636363</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>10</v>
@@ -2288,7 +2280,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>20</v>
@@ -2320,7 +2312,7 @@
         <v>135.66666666666666</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>10</v>
@@ -2365,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>10</v>
@@ -2410,7 +2402,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>10</v>
@@ -2455,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>10</v>
@@ -2501,7 +2493,7 @@
         <v>14</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>10</v>
@@ -2546,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>10</v>
@@ -2591,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>10</v>
@@ -2636,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>10</v>
@@ -2681,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>10</v>
@@ -2726,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>10</v>
@@ -2771,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>10</v>
@@ -2816,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>10</v>
@@ -2861,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>10</v>
@@ -2906,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>10</v>
@@ -2951,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>10</v>
@@ -2996,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>10</v>
@@ -3041,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>10</v>
@@ -3086,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>10</v>
@@ -3131,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>10</v>
@@ -3176,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>10</v>
@@ -3221,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>10</v>
@@ -3266,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>10</v>
@@ -3311,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>10</v>
@@ -3356,7 +3348,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>10</v>
@@ -3401,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>10</v>
@@ -3446,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>10</v>
@@ -3491,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>10</v>
@@ -3536,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>10</v>
@@ -3581,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>10</v>
@@ -3626,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>10</v>
@@ -3671,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>10</v>
@@ -3716,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>10</v>
@@ -3730,7 +3722,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>75</v>
@@ -3775,7 +3767,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>78</v>
@@ -3800,7 +3792,7 @@
         <v>103.5</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J37" s="5">
         <v>0.5</v>
@@ -3820,7 +3812,7 @@
     </row>
     <row r="38" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>79</v>
@@ -3851,7 +3843,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>10</v>
@@ -3865,7 +3857,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>82</v>
@@ -3897,13 +3889,13 @@
         <v>0.97809719370294324</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M39" s="3" t="s">
-        <v>436</v>
+      <c r="M39" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>83</v>
@@ -3911,7 +3903,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>84</v>
@@ -3942,7 +3934,7 @@
         <v>18</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>10</v>
@@ -3956,7 +3948,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>87</v>
@@ -3988,7 +3980,7 @@
         <v>32</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>10</v>
@@ -4002,10 +3994,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>437</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>47</v>
@@ -4033,7 +4025,7 @@
         <v>44</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>10</v>
@@ -4047,10 +4039,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>437</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>47</v>
@@ -4078,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>10</v>
@@ -4092,10 +4084,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>90</v>
@@ -4124,7 +4116,7 @@
         <v>9.7365553308998543</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>10</v>
@@ -4138,7 +4130,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>93</v>
@@ -4169,7 +4161,7 @@
         <v>13</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L45" s="9" t="s">
         <v>23</v>
@@ -4183,7 +4175,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>95</v>
@@ -4214,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L46" s="9" t="s">
         <v>23</v>
@@ -4228,7 +4220,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B47" s="15" t="s">
         <v>99</v>
@@ -4258,7 +4250,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>100</v>
@@ -4272,7 +4264,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B48" s="15" t="s">
         <v>102</v>
@@ -4302,7 +4294,7 @@
         <v>4.8</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>100</v>
@@ -4316,7 +4308,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B49" s="15" t="s">
         <v>98</v>
@@ -4346,7 +4338,7 @@
         <v>1.48</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>100</v>
@@ -4360,7 +4352,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B50" s="15" t="s">
         <v>97</v>
@@ -4390,7 +4382,7 @@
         <v>1.51</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>100</v>
@@ -4404,7 +4396,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B51" s="15" t="s">
         <v>103</v>
@@ -4434,7 +4426,7 @@
         <v>1.06</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>100</v>
@@ -4448,7 +4440,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B52" s="15" t="s">
         <v>104</v>
@@ -4478,7 +4470,7 @@
         <v>0.35</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>100</v>
@@ -4492,7 +4484,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B53" s="15" t="s">
         <v>105</v>
@@ -4522,7 +4514,7 @@
         <v>3</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>100</v>
@@ -4536,7 +4528,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>107</v>
@@ -4567,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>10</v>
@@ -4581,7 +4573,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>109</v>
@@ -4612,7 +4604,7 @@
         <v>1</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>10</v>
@@ -4626,7 +4618,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>110</v>
@@ -4657,7 +4649,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>10</v>
@@ -4671,7 +4663,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>111</v>
@@ -4703,7 +4695,7 @@
         <v>18</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>10</v>
@@ -4717,7 +4709,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>113</v>
@@ -4748,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>10</v>
@@ -4762,7 +4754,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>114</v>
@@ -4793,7 +4785,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>10</v>
@@ -4807,7 +4799,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>116</v>
@@ -4839,7 +4831,7 @@
         <v>0.39698836413415467</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>10</v>
@@ -4853,7 +4845,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>119</v>
@@ -4885,7 +4877,7 @@
         <v>0.625</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>23</v>
@@ -4899,7 +4891,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>122</v>
@@ -4930,7 +4922,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>10</v>
@@ -4944,7 +4936,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>126</v>
@@ -4976,7 +4968,7 @@
         <v>0.91991786447638602</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>10</v>
@@ -4990,7 +4982,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>129</v>
@@ -5022,7 +5014,7 @@
         <v>0.99726027397260275</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>100</v>
@@ -5036,7 +5028,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>133</v>
@@ -5068,7 +5060,7 @@
         <v>0.99726027397260275</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>100</v>
@@ -5082,7 +5074,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>134</v>
@@ -5113,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>10</v>
@@ -5127,7 +5119,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>136</v>
@@ -5158,7 +5150,7 @@
         <v>1</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>10</v>
@@ -5172,7 +5164,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>137</v>
@@ -5203,7 +5195,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L68" s="3" t="s">
         <v>10</v>
@@ -5217,10 +5209,10 @@
     </row>
     <row r="69" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="31" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B69" s="32" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C69" s="32" t="s">
         <v>138</v>
@@ -5248,24 +5240,24 @@
         <v>34</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>140</v>
+        <v>501</v>
       </c>
       <c r="M69" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N69" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="31" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C70" s="32" t="s">
         <v>47</v>
@@ -5287,13 +5279,13 @@
         <v>30</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J70" s="5">
         <v>39</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>10</v>
@@ -5302,15 +5294,15 @@
         <v>16</v>
       </c>
       <c r="N70" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="71" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="31" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B71" s="32" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C71" s="32" t="s">
         <v>47</v>
@@ -5332,14 +5324,14 @@
         <v>24</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="J71" s="5">
         <f>48+22+14</f>
         <v>84</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L71" s="3" t="s">
         <v>10</v>
@@ -5348,15 +5340,15 @@
         <v>16</v>
       </c>
       <c r="N71" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="31" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B72" s="32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C72" s="32" t="s">
         <v>47</v>
@@ -5378,14 +5370,14 @@
         <v>3</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J72" s="5">
         <f>148</f>
         <v>148</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>10</v>
@@ -5394,15 +5386,15 @@
         <v>16</v>
       </c>
       <c r="N72" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="31" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B73" s="32" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C73" s="32" t="s">
         <v>47</v>
@@ -5430,7 +5422,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L73" s="3" t="s">
         <v>10</v>
@@ -5439,15 +5431,15 @@
         <v>16</v>
       </c>
       <c r="N73" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="74" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="31" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B74" s="32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C74" s="32" t="s">
         <v>47</v>
@@ -5475,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L74" s="3" t="s">
         <v>10</v>
@@ -5484,18 +5476,18 @@
         <v>16</v>
       </c>
       <c r="N74" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="75" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="31" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B75" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C75" s="32" t="s">
         <v>149</v>
-      </c>
-      <c r="C75" s="32" t="s">
-        <v>150</v>
       </c>
       <c r="D75" s="5">
         <v>53.890380999999998</v>
@@ -5520,7 +5512,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L75" s="3" t="s">
         <v>10</v>
@@ -5529,18 +5521,18 @@
         <v>16</v>
       </c>
       <c r="N75" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="31" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B76" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C76" s="32" t="s">
         <v>149</v>
-      </c>
-      <c r="C76" s="32" t="s">
-        <v>150</v>
       </c>
       <c r="D76" s="5">
         <v>53.890380999999998</v>
@@ -5565,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>10</v>
@@ -5574,15 +5566,15 @@
         <v>16</v>
       </c>
       <c r="N76" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="31" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B77" s="32" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C77" s="32" t="s">
         <v>26</v>
@@ -5610,7 +5602,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L77" s="9" t="s">
         <v>23</v>
@@ -5619,15 +5611,15 @@
         <v>16</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="78" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="31" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B78" s="32" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C78" s="32" t="s">
         <v>26</v>
@@ -5655,7 +5647,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L78" s="9" t="s">
         <v>23</v>
@@ -5664,15 +5656,15 @@
         <v>16</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="31" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B79" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C79" s="32" t="s">
         <v>26</v>
@@ -5700,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L79" s="9" t="s">
         <v>23</v>
@@ -5709,15 +5701,15 @@
         <v>16</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="80" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="31" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B80" s="32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C80" s="32" t="s">
         <v>26</v>
@@ -5745,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L80" s="9" t="s">
         <v>23</v>
@@ -5754,15 +5746,15 @@
         <v>16</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="81" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="31" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B81" s="32" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C81" s="32" t="s">
         <v>26</v>
@@ -5784,13 +5776,13 @@
         <v>45</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="J81" s="5">
         <v>9</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L81" s="9" t="s">
         <v>23</v>
@@ -5799,15 +5791,15 @@
         <v>16</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="82" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="31" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B82" s="32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C82" s="32" t="s">
         <v>80</v>
@@ -5844,15 +5836,15 @@
         <v>16</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="31" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B83" s="32" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C83" s="32" t="s">
         <v>80</v>
@@ -5889,18 +5881,18 @@
         <v>16</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="84" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="31" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B84" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C84" s="32" t="s">
         <v>160</v>
-      </c>
-      <c r="C84" s="32" t="s">
-        <v>161</v>
       </c>
       <c r="D84" s="8">
         <v>38.296666999999999</v>
@@ -5925,7 +5917,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L84" s="9" t="s">
         <v>23</v>
@@ -5934,18 +5926,18 @@
         <v>16</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="31" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B85" s="32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C85" s="32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D85" s="5">
         <v>35.646303000000003</v>
@@ -5970,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L85" s="9" t="s">
         <v>23</v>
@@ -5979,18 +5971,18 @@
         <v>16</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="31" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B86" s="32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C86" s="32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D86" s="5">
         <v>35.456859000000001</v>
@@ -6015,7 +6007,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L86" s="9" t="s">
         <v>23</v>
@@ -6024,15 +6016,15 @@
         <v>16</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="87" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="31" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B87" s="32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C87" s="32" t="s">
         <v>22</v>
@@ -6054,7 +6046,7 @@
         <v>113</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="J87" s="5">
         <v>2</v>
@@ -6069,15 +6061,15 @@
         <v>16</v>
       </c>
       <c r="N87" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="31" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B88" s="32" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C88" s="32" t="s">
         <v>37</v>
@@ -6105,7 +6097,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L88" s="9" t="s">
         <v>23</v>
@@ -6114,15 +6106,15 @@
         <v>16</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>22</v>
@@ -6144,30 +6136,30 @@
         <v>29</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J89" s="5">
         <v>5</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>449</v>
+        <v>501</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N89" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>22</v>
@@ -6195,7 +6187,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L90" s="3" t="s">
         <v>10</v>
@@ -6204,15 +6196,15 @@
         <v>86</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>22</v>
@@ -6240,7 +6232,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>10</v>
@@ -6249,15 +6241,15 @@
         <v>86</v>
       </c>
       <c r="N91" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>22</v>
@@ -6279,31 +6271,31 @@
         <v>17</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="J92" s="5">
         <f>4</f>
         <v>4</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>449</v>
+        <v>501</v>
       </c>
       <c r="M92" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>22</v>
@@ -6331,7 +6323,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L93" s="3" t="s">
         <v>10</v>
@@ -6340,15 +6332,15 @@
         <v>86</v>
       </c>
       <c r="N93" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>47</v>
@@ -6376,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>10</v>
@@ -6385,15 +6377,15 @@
         <v>16</v>
       </c>
       <c r="N94" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>47</v>
@@ -6415,13 +6407,13 @@
         <v>100</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J95" s="5">
         <v>4</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L95" s="3" t="s">
         <v>100</v>
@@ -6430,15 +6422,15 @@
         <v>16</v>
       </c>
       <c r="N95" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>47</v>
@@ -6460,13 +6452,13 @@
         <v>100</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J96" s="5">
         <v>4</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>10</v>
@@ -6475,15 +6467,15 @@
         <v>16</v>
       </c>
       <c r="N96" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>25</v>
@@ -6511,24 +6503,24 @@
         <v>0</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>452</v>
+        <v>502</v>
       </c>
       <c r="M97" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="N97" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="N97" s="6" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>25</v>
@@ -6556,24 +6548,24 @@
         <v>0</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>452</v>
+        <v>502</v>
       </c>
       <c r="M98" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="N98" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="N98" s="6" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>25</v>
@@ -6601,24 +6593,24 @@
         <v>0</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>452</v>
+        <v>502</v>
       </c>
       <c r="M99" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="N99" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="N99" s="6" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>25</v>
@@ -6646,24 +6638,24 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>452</v>
+        <v>502</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>47</v>
@@ -6685,30 +6677,30 @@
         <v>63</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="J101" s="5">
         <v>42</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M101" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="N101" s="7" t="s">
         <v>185</v>
-      </c>
-      <c r="N101" s="7" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>47</v>
@@ -6730,30 +6722,30 @@
         <v>23</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="J102" s="5">
         <v>10</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L102" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="N102" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>22</v>
@@ -6775,13 +6767,13 @@
         <v>37</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="J103" s="5">
         <v>29</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L103" s="3" t="s">
         <v>10</v>
@@ -6790,15 +6782,15 @@
         <v>16</v>
       </c>
       <c r="N103" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>22</v>
@@ -6820,14 +6812,14 @@
         <v>90</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="J104" s="5">
         <f>17+22</f>
         <v>39</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L104" s="3" t="s">
         <v>10</v>
@@ -6836,15 +6828,15 @@
         <v>16</v>
       </c>
       <c r="N104" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>22</v>
@@ -6872,24 +6864,24 @@
         <v>0</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L105" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M105" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N105" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N105" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>22</v>
@@ -6911,30 +6903,30 @@
         <v>19</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J106" s="5">
         <v>58</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L106" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M106" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N106" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N106" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>22</v>
@@ -6962,24 +6954,24 @@
         <v>0</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L107" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M107" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N107" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N107" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>22</v>
@@ -7007,24 +6999,24 @@
         <v>0</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L108" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M108" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N108" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N108" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>22</v>
@@ -7046,30 +7038,30 @@
         <v>71</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="J109" s="5">
         <v>38</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L109" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M109" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N109" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N109" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>22</v>
@@ -7091,30 +7083,30 @@
         <v>170</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="J110" s="5">
         <v>5</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L110" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M110" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N110" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N110" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>22</v>
@@ -7142,24 +7134,24 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L111" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M111" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N111" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N111" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>22</v>
@@ -7181,30 +7173,30 @@
         <v>60</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="J112" s="5">
         <v>71</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L112" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M112" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N112" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N112" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>22</v>
@@ -7226,30 +7218,30 @@
         <v>10</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="J113" s="5">
         <v>59</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L113" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M113" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N113" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N113" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>22</v>
@@ -7271,30 +7263,30 @@
         <v>31</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="J114" s="5">
         <v>73</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L114" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M114" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N114" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N114" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>22</v>
@@ -7316,30 +7308,30 @@
         <v>36</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J115" s="5">
         <v>20</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L115" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M115" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N115" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N115" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>22</v>
@@ -7361,30 +7353,30 @@
         <v>53</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="J116" s="5">
         <v>2</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L116" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M116" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N116" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N116" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>22</v>
@@ -7412,24 +7404,24 @@
         <v>0</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L117" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M117" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N117" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N117" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>22</v>
@@ -7457,24 +7449,24 @@
         <v>0</v>
       </c>
       <c r="K118" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L118" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M118" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N118" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N118" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>22</v>
@@ -7502,24 +7494,24 @@
         <v>0</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L119" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M119" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N119" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N119" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>22</v>
@@ -7547,24 +7539,24 @@
         <v>0</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L120" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M120" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N120" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N120" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>22</v>
@@ -7592,24 +7584,24 @@
         <v>0</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L121" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M121" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N121" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N121" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>22</v>
@@ -7637,24 +7629,24 @@
         <v>0</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L122" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M122" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N122" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N122" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>22</v>
@@ -7682,24 +7674,24 @@
         <v>0</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L123" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M123" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N123" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N123" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>22</v>
@@ -7727,24 +7719,24 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L124" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M124" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N124" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N124" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>22</v>
@@ -7772,24 +7764,24 @@
         <v>0</v>
       </c>
       <c r="K125" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L125" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M125" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N125" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N125" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>22</v>
@@ -7817,24 +7809,24 @@
         <v>0</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L126" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M126" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N126" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N126" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>22</v>
@@ -7856,30 +7848,30 @@
         <v>37</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="J127" s="5">
         <v>37</v>
       </c>
       <c r="K127" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L127" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M127" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N127" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N127" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>22</v>
@@ -7901,30 +7893,30 @@
         <v>5</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="J128" s="5">
         <v>34</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L128" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M128" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N128" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N128" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>22</v>
@@ -7946,30 +7938,30 @@
         <v>79</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="J129" s="5">
         <v>19</v>
       </c>
       <c r="K129" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L129" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M129" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N129" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N129" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>22</v>
@@ -7991,30 +7983,30 @@
         <v>23</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J130" s="5">
         <v>54</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L130" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M130" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N130" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N130" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>22</v>
@@ -8042,24 +8034,24 @@
         <v>0</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L131" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M131" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N131" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N131" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>22</v>
@@ -8087,24 +8079,24 @@
         <v>0</v>
       </c>
       <c r="K132" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L132" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M132" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N132" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N132" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>22</v>
@@ -8132,24 +8124,24 @@
         <v>0</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L133" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M133" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N133" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N133" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>22</v>
@@ -8171,30 +8163,30 @@
         <v>11</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="J134" s="5">
         <v>87</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L134" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M134" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N134" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N134" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>22</v>
@@ -8222,24 +8214,24 @@
         <v>25</v>
       </c>
       <c r="K135" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L135" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M135" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N135" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N135" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>22</v>
@@ -8267,24 +8259,24 @@
         <v>0</v>
       </c>
       <c r="K136" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L136" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M136" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N136" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N136" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>22</v>
@@ -8312,24 +8304,24 @@
         <v>0</v>
       </c>
       <c r="K137" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L137" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M137" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N137" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N137" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>22</v>
@@ -8351,30 +8343,30 @@
         <v>6</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J138" s="5">
         <v>30</v>
       </c>
       <c r="K138" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L138" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M138" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N138" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N138" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>22</v>
@@ -8396,31 +8388,31 @@
         <v>43</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="J139" s="5">
         <f>16+8+15+12</f>
         <v>51</v>
       </c>
       <c r="K139" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L139" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M139" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N139" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N139" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>22</v>
@@ -8442,30 +8434,30 @@
         <v>40</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J140" s="5">
         <v>6</v>
       </c>
       <c r="K140" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L140" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M140" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N140" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N140" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>22</v>
@@ -8493,24 +8485,24 @@
         <v>0</v>
       </c>
       <c r="K141" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L141" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M141" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N141" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N141" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>22</v>
@@ -8538,24 +8530,24 @@
         <v>0</v>
       </c>
       <c r="K142" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L142" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M142" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N142" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N142" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>22</v>
@@ -8583,24 +8575,24 @@
         <v>0</v>
       </c>
       <c r="K143" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L143" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M143" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N143" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N143" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>22</v>
@@ -8628,24 +8620,24 @@
         <v>0</v>
       </c>
       <c r="K144" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L144" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M144" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="145" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>22</v>
@@ -8673,24 +8665,24 @@
         <v>0</v>
       </c>
       <c r="K145" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L145" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M145" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N145" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="146" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>22</v>
@@ -8718,24 +8710,24 @@
         <v>0</v>
       </c>
       <c r="K146" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L146" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M146" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="147" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>22</v>
@@ -8763,24 +8755,24 @@
         <v>0</v>
       </c>
       <c r="K147" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L147" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M147" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N147" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="148" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>22</v>
@@ -8808,24 +8800,24 @@
         <v>0</v>
       </c>
       <c r="K148" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L148" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M148" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="149" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>22</v>
@@ -8853,7 +8845,7 @@
         <v>0</v>
       </c>
       <c r="K149" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L149" s="3" t="s">
         <v>10</v>
@@ -8862,15 +8854,15 @@
         <v>86</v>
       </c>
       <c r="N149" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="150" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>47</v>
@@ -8898,7 +8890,7 @@
         <v>0</v>
       </c>
       <c r="K150" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L150" s="3" t="s">
         <v>10</v>
@@ -8907,15 +8899,15 @@
         <v>23</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="151" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>22</v>
@@ -8937,13 +8929,13 @@
         <v>2</v>
       </c>
       <c r="I151" s="3" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="J151" s="5">
         <v>32</v>
       </c>
       <c r="K151" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L151" s="3" t="s">
         <v>10</v>
@@ -8952,15 +8944,15 @@
         <v>23</v>
       </c>
       <c r="N151" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="152" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>22</v>
@@ -8982,13 +8974,13 @@
         <v>2</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="J152" s="5">
         <v>18</v>
       </c>
       <c r="K152" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L152" s="3" t="s">
         <v>10</v>
@@ -8997,15 +8989,15 @@
         <v>23</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>22</v>
@@ -9033,7 +9025,7 @@
         <v>0</v>
       </c>
       <c r="K153" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L153" s="3" t="s">
         <v>10</v>
@@ -9042,15 +9034,15 @@
         <v>23</v>
       </c>
       <c r="N153" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>22</v>
@@ -9078,7 +9070,7 @@
         <v>0</v>
       </c>
       <c r="K154" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L154" s="3" t="s">
         <v>10</v>
@@ -9087,15 +9079,15 @@
         <v>23</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="155" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>22</v>
@@ -9123,7 +9115,7 @@
         <v>0</v>
       </c>
       <c r="K155" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L155" s="3" t="s">
         <v>10</v>
@@ -9132,15 +9124,15 @@
         <v>23</v>
       </c>
       <c r="N155" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>22</v>
@@ -9168,7 +9160,7 @@
         <v>0</v>
       </c>
       <c r="K156" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L156" s="3" t="s">
         <v>10</v>
@@ -9177,15 +9169,15 @@
         <v>23</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="157" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A157" s="14" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B157" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>96</v>
@@ -9207,13 +9199,13 @@
         <v>50</v>
       </c>
       <c r="I157" s="9" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="J157" s="10">
         <v>12</v>
       </c>
       <c r="K157" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L157" s="3" t="s">
         <v>10</v>
@@ -9222,7 +9214,7 @@
         <v>86</v>
       </c>
       <c r="N157" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O157" s="11"/>
       <c r="P157" s="11"/>
@@ -9235,10 +9227,10 @@
     </row>
     <row r="158" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A158" s="14" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>96</v>
@@ -9260,13 +9252,13 @@
         <v>21</v>
       </c>
       <c r="I158" s="9" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="J158" s="10">
         <v>3</v>
       </c>
       <c r="K158" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L158" s="9" t="s">
         <v>23</v>
@@ -9275,7 +9267,7 @@
         <v>86</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O158" s="11"/>
       <c r="P158" s="11"/>
@@ -9288,10 +9280,10 @@
     </row>
     <row r="159" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A159" s="14" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B159" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>96</v>
@@ -9319,7 +9311,7 @@
         <v>0</v>
       </c>
       <c r="K159" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L159" s="9" t="s">
         <v>23</v>
@@ -9328,7 +9320,7 @@
         <v>86</v>
       </c>
       <c r="N159" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O159" s="11"/>
       <c r="P159" s="11"/>
@@ -9341,10 +9333,10 @@
     </row>
     <row r="160" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A160" s="14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>22</v>
@@ -9366,22 +9358,22 @@
         <v>7</v>
       </c>
       <c r="I160" s="9" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="J160" s="10">
         <v>24</v>
       </c>
       <c r="K160" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L160" s="9" t="s">
         <v>23</v>
       </c>
       <c r="M160" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="N160" s="7" t="s">
         <v>256</v>
-      </c>
-      <c r="N160" s="7" t="s">
-        <v>257</v>
       </c>
       <c r="O160" s="11"/>
       <c r="P160" s="11"/>
@@ -9394,10 +9386,10 @@
     </row>
     <row r="161" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A161" s="14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>22</v>
@@ -9419,22 +9411,22 @@
         <v>1.42</v>
       </c>
       <c r="I161" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J161" s="10">
         <v>1.58</v>
       </c>
       <c r="K161" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L161" s="9" t="s">
         <v>23</v>
       </c>
       <c r="M161" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N161" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O161" s="11"/>
       <c r="P161" s="11"/>
@@ -9447,10 +9439,10 @@
     </row>
     <row r="162" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A162" s="14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>22</v>
@@ -9472,7 +9464,7 @@
         <v>8.9000000000000057</v>
       </c>
       <c r="I162" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J162" s="10">
         <v>68.099999999999994</v>
@@ -9484,10 +9476,10 @@
         <v>23</v>
       </c>
       <c r="M162" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N162" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O162" s="11"/>
       <c r="P162" s="11"/>
@@ -9500,7 +9492,7 @@
     </row>
     <row r="163" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>24</v>
@@ -9531,21 +9523,21 @@
         <v>0</v>
       </c>
       <c r="K163" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L163" s="3" t="s">
-        <v>476</v>
+        <v>501</v>
       </c>
       <c r="M163" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="N163" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="N163" s="6" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="164" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>24</v>
@@ -9570,13 +9562,13 @@
         <v>20</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="J164" s="5">
         <v>3</v>
       </c>
       <c r="K164" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L164" s="3" t="s">
         <v>10</v>
@@ -9585,15 +9577,15 @@
         <v>86</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="165" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>22</v>
@@ -9615,30 +9607,30 @@
         <v>33</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J165" s="5">
         <v>0</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L165" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M165" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N165" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="166" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>22</v>
@@ -9666,7 +9658,7 @@
         <v>0</v>
       </c>
       <c r="K166" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L166" s="3" t="s">
         <v>10</v>
@@ -9675,15 +9667,15 @@
         <v>16</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="167" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>22</v>
@@ -9711,7 +9703,7 @@
         <v>0</v>
       </c>
       <c r="K167" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L167" s="3" t="s">
         <v>10</v>
@@ -9720,15 +9712,15 @@
         <v>16</v>
       </c>
       <c r="N167" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="168" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>47</v>
@@ -9750,14 +9742,14 @@
         <v>5</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="J168" s="5">
         <f>98+33</f>
         <v>131</v>
       </c>
       <c r="K168" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L168" s="3" t="s">
         <v>10</v>
@@ -9766,15 +9758,15 @@
         <v>23</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="169" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>47</v>
@@ -9796,30 +9788,30 @@
         <v>24</v>
       </c>
       <c r="I169" s="3" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="J169" s="5">
         <v>56</v>
       </c>
       <c r="K169" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L169" s="3" t="s">
         <v>100</v>
       </c>
       <c r="M169" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N169" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="170" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>47</v>
@@ -9847,7 +9839,7 @@
         <v>0</v>
       </c>
       <c r="K170" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L170" s="3" t="s">
         <v>10</v>
@@ -9856,15 +9848,15 @@
         <v>23</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="171" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>47</v>
@@ -9886,31 +9878,31 @@
         <v>8</v>
       </c>
       <c r="I171" s="3" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="J171" s="5">
         <f>31+20+6</f>
         <v>57</v>
       </c>
       <c r="K171" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L171" s="3" t="s">
         <v>100</v>
       </c>
       <c r="M171" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N171" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="172" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>47</v>
@@ -9932,13 +9924,13 @@
         <v>2</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J172" s="5">
         <v>19</v>
       </c>
       <c r="K172" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L172" s="3" t="s">
         <v>10</v>
@@ -9947,15 +9939,15 @@
         <v>23</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="173" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>47</v>
@@ -9977,31 +9969,31 @@
         <v>11</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="J173" s="5">
         <f>1+30+1+18+4+4</f>
         <v>58</v>
       </c>
       <c r="K173" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L173" s="3" t="s">
         <v>100</v>
       </c>
       <c r="M173" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N173" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="174" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>123</v>
@@ -10029,24 +10021,24 @@
         <v>0</v>
       </c>
       <c r="K174" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L174" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M174" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="N174" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="N174" s="6" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="175" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>123</v>
@@ -10068,31 +10060,31 @@
         <v>47.917864476386036</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="J175" s="5">
         <f>3+(30/365.25)</f>
         <v>3.0821355236139629</v>
       </c>
       <c r="K175" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L175" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M175" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N175" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="176" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>123</v>
@@ -10114,14 +10106,14 @@
         <v>51.915126625598901</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="J176" s="5">
         <f>3+((31+30+31+30)/365.25)+4-((30+31+30)/365.25)+4</f>
         <v>11.084873374401095</v>
       </c>
       <c r="K176" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L176" s="3" t="s">
         <v>10</v>
@@ -10130,15 +10122,15 @@
         <v>16</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="177" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B177" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>123</v>
@@ -10166,24 +10158,24 @@
         <v>0</v>
       </c>
       <c r="K177" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L177" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M177" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N177" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="178" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>123</v>
@@ -10211,7 +10203,7 @@
         <v>0</v>
       </c>
       <c r="K178" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L178" s="3" t="s">
         <v>10</v>
@@ -10220,15 +10212,15 @@
         <v>16</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="179" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>123</v>
@@ -10250,30 +10242,30 @@
         <v>44</v>
       </c>
       <c r="I179" s="3" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="J179" s="5">
         <v>5</v>
       </c>
       <c r="K179" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L179" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M179" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N179" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="180" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>123</v>
@@ -10301,24 +10293,24 @@
         <v>0</v>
       </c>
       <c r="K180" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L180" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M180" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="181" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C181" s="3" t="s">
         <v>123</v>
@@ -10346,24 +10338,24 @@
         <v>0</v>
       </c>
       <c r="K181" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L181" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M181" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N181" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="182" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>25</v>
@@ -10385,30 +10377,30 @@
         <v>4</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="J182" s="5">
         <v>49</v>
       </c>
       <c r="K182" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="M182" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="N182" s="6" t="s">
         <v>288</v>
-      </c>
-      <c r="N182" s="6" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="183" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C183" s="3" t="s">
         <v>22</v>
@@ -10436,7 +10428,7 @@
         <v>0</v>
       </c>
       <c r="K183" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L183" s="3" t="s">
         <v>10</v>
@@ -10445,7 +10437,7 @@
         <v>16</v>
       </c>
       <c r="N183" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O183" s="11"/>
       <c r="P183" s="11"/>
@@ -10458,10 +10450,10 @@
     </row>
     <row r="184" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C184" s="3" t="s">
         <v>22</v>
@@ -10489,7 +10481,7 @@
         <v>0</v>
       </c>
       <c r="K184" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L184" s="3" t="s">
         <v>10</v>
@@ -10498,7 +10490,7 @@
         <v>86</v>
       </c>
       <c r="N184" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O184" s="11"/>
       <c r="P184" s="11"/>
@@ -10511,10 +10503,10 @@
     </row>
     <row r="185" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>22</v>
@@ -10536,13 +10528,13 @@
         <v>24</v>
       </c>
       <c r="I185" s="3" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="J185" s="5">
         <v>17</v>
       </c>
       <c r="K185" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L185" s="3" t="s">
         <v>10</v>
@@ -10551,7 +10543,7 @@
         <v>86</v>
       </c>
       <c r="N185" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O185" s="11"/>
       <c r="P185" s="11"/>
@@ -10564,10 +10556,10 @@
     </row>
     <row r="186" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>22</v>
@@ -10589,13 +10581,13 @@
         <v>2</v>
       </c>
       <c r="I186" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="J186" s="5">
         <v>12</v>
       </c>
       <c r="K186" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L186" s="3" t="s">
         <v>10</v>
@@ -10604,7 +10596,7 @@
         <v>23</v>
       </c>
       <c r="N186" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O186" s="11"/>
       <c r="P186" s="11"/>
@@ -10617,10 +10609,10 @@
     </row>
     <row r="187" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C187" s="3" t="s">
         <v>14</v>
@@ -10648,7 +10640,7 @@
         <v>0.75</v>
       </c>
       <c r="K187" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L187" s="3" t="s">
         <v>10</v>
@@ -10657,7 +10649,7 @@
         <v>16</v>
       </c>
       <c r="N187" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O187" s="11"/>
       <c r="P187" s="11"/>
@@ -10670,10 +10662,10 @@
     </row>
     <row r="188" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C188" s="3" t="s">
         <v>14</v>
@@ -10701,7 +10693,7 @@
         <v>0</v>
       </c>
       <c r="K188" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L188" s="3" t="s">
         <v>10</v>
@@ -10710,7 +10702,7 @@
         <v>16</v>
       </c>
       <c r="N188" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O188" s="11"/>
       <c r="P188" s="11"/>
@@ -10723,10 +10715,10 @@
     </row>
     <row r="189" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>25</v>
@@ -10754,7 +10746,7 @@
         <v>1</v>
       </c>
       <c r="K189" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L189" s="3" t="s">
         <v>10</v>
@@ -10763,15 +10755,15 @@
         <v>86</v>
       </c>
       <c r="N189" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="190" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C190" s="3" t="s">
         <v>25</v>
@@ -10799,7 +10791,7 @@
         <v>1</v>
       </c>
       <c r="K190" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L190" s="3" t="s">
         <v>10</v>
@@ -10808,15 +10800,15 @@
         <v>86</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="191" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C191" s="3" t="s">
         <v>25</v>
@@ -10844,7 +10836,7 @@
         <v>0</v>
       </c>
       <c r="K191" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L191" s="3" t="s">
         <v>10</v>
@@ -10853,15 +10845,15 @@
         <v>86</v>
       </c>
       <c r="N191" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="192" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C192" s="3" t="s">
         <v>25</v>
@@ -10889,7 +10881,7 @@
         <v>0</v>
       </c>
       <c r="K192" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L192" s="3" t="s">
         <v>10</v>
@@ -10898,15 +10890,15 @@
         <v>86</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C193" s="3" t="s">
         <v>25</v>
@@ -10934,7 +10926,7 @@
         <v>0</v>
       </c>
       <c r="K193" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L193" s="3" t="s">
         <v>10</v>
@@ -10943,15 +10935,15 @@
         <v>86</v>
       </c>
       <c r="N193" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>25</v>
@@ -10979,7 +10971,7 @@
         <v>0</v>
       </c>
       <c r="K194" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L194" s="3" t="s">
         <v>10</v>
@@ -10988,15 +10980,15 @@
         <v>86</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>25</v>
@@ -11018,13 +11010,13 @@
         <v>36</v>
       </c>
       <c r="I195" s="3" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="J195" s="5">
         <v>40</v>
       </c>
       <c r="K195" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L195" s="3" t="s">
         <v>10</v>
@@ -11033,15 +11025,15 @@
         <v>86</v>
       </c>
       <c r="N195" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>25</v>
@@ -11069,7 +11061,7 @@
         <v>0</v>
       </c>
       <c r="K196" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L196" s="3" t="s">
         <v>10</v>
@@ -11078,15 +11070,15 @@
         <v>86</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C197" s="3" t="s">
         <v>25</v>
@@ -11114,7 +11106,7 @@
         <v>0</v>
       </c>
       <c r="K197" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L197" s="3" t="s">
         <v>10</v>
@@ -11123,15 +11115,15 @@
         <v>86</v>
       </c>
       <c r="N197" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C198" s="3" t="s">
         <v>25</v>
@@ -11159,7 +11151,7 @@
         <v>0</v>
       </c>
       <c r="K198" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L198" s="3" t="s">
         <v>10</v>
@@ -11168,15 +11160,15 @@
         <v>86</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C199" s="3" t="s">
         <v>25</v>
@@ -11204,7 +11196,7 @@
         <v>0</v>
       </c>
       <c r="K199" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L199" s="3" t="s">
         <v>10</v>
@@ -11213,15 +11205,15 @@
         <v>86</v>
       </c>
       <c r="N199" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A200" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>25</v>
@@ -11250,7 +11242,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="K200" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L200" s="3" t="s">
         <v>10</v>
@@ -11259,15 +11251,15 @@
         <v>86</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C201" s="3" t="s">
         <v>25</v>
@@ -11295,7 +11287,7 @@
         <v>0</v>
       </c>
       <c r="K201" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L201" s="3" t="s">
         <v>10</v>
@@ -11304,15 +11296,15 @@
         <v>86</v>
       </c>
       <c r="N201" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C202" s="3" t="s">
         <v>25</v>
@@ -11340,7 +11332,7 @@
         <v>0</v>
       </c>
       <c r="K202" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L202" s="3" t="s">
         <v>10</v>
@@ -11349,15 +11341,15 @@
         <v>86</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C203" s="3" t="s">
         <v>25</v>
@@ -11385,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="K203" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L203" s="3" t="s">
         <v>10</v>
@@ -11394,15 +11386,15 @@
         <v>86</v>
       </c>
       <c r="N203" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>47</v>
@@ -11424,31 +11416,31 @@
         <v>54.5</v>
       </c>
       <c r="I204" s="3" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="J204" s="5">
         <f>6+0.5+2</f>
         <v>8.5</v>
       </c>
       <c r="K204" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L204" s="3" t="s">
         <v>100</v>
       </c>
       <c r="M204" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="N204" s="7" t="s">
         <v>312</v>
-      </c>
-      <c r="N204" s="7" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C205" s="3" t="s">
         <v>47</v>
@@ -11476,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="K205" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L205" s="3" t="s">
         <v>10</v>
@@ -11485,18 +11477,18 @@
         <v>16</v>
       </c>
       <c r="N205" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B206" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="C206" s="3" t="s">
         <v>314</v>
-      </c>
-      <c r="C206" s="3" t="s">
-        <v>315</v>
       </c>
       <c r="D206" s="5">
         <v>5.3038499999999997</v>
@@ -11521,7 +11513,7 @@
         <v>0</v>
       </c>
       <c r="K206" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L206" s="3" t="s">
         <v>100</v>
@@ -11530,15 +11522,15 @@
         <v>16</v>
       </c>
       <c r="N206" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C207" s="3" t="s">
         <v>26</v>
@@ -11560,30 +11552,30 @@
         <v>35</v>
       </c>
       <c r="I207" s="3" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="J207" s="5">
         <v>4</v>
       </c>
       <c r="K207" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L207" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="M207" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N207" s="18" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C208" s="3" t="s">
         <v>26</v>
@@ -11605,13 +11597,13 @@
         <v>91</v>
       </c>
       <c r="I208" s="3" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="J208" s="5">
         <v>4</v>
       </c>
       <c r="K208" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L208" s="3" t="s">
         <v>10</v>
@@ -11620,15 +11612,15 @@
         <v>86</v>
       </c>
       <c r="N208" s="18" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B209" s="19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C209" s="3" t="s">
         <v>14</v>
@@ -11657,24 +11649,24 @@
         <v>2.6468172484599588</v>
       </c>
       <c r="K209" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L209" s="3" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="M209" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N209" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B210" s="20" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C210" s="3" t="s">
         <v>22</v>
@@ -11703,7 +11695,7 @@
         <v>31</v>
       </c>
       <c r="K210" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L210" s="3" t="s">
         <v>10</v>
@@ -11712,15 +11704,15 @@
         <v>86</v>
       </c>
       <c r="N210" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B211" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>22</v>
@@ -11749,7 +11741,7 @@
         <v>2</v>
       </c>
       <c r="K211" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L211" s="3" t="s">
         <v>10</v>
@@ -11758,15 +11750,15 @@
         <v>86</v>
       </c>
       <c r="N211" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B212" s="20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C212" s="3" t="s">
         <v>22</v>
@@ -11795,7 +11787,7 @@
         <v>2.8999999999999986</v>
       </c>
       <c r="K212" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L212" s="3" t="s">
         <v>10</v>
@@ -11804,15 +11796,15 @@
         <v>86</v>
       </c>
       <c r="N212" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B213" s="20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C213" s="3" t="s">
         <v>22</v>
@@ -11841,7 +11833,7 @@
         <v>20.099999999999994</v>
       </c>
       <c r="K213" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L213" s="3" t="s">
         <v>10</v>
@@ -11850,15 +11842,15 @@
         <v>86</v>
       </c>
       <c r="N213" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B214" s="20" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C214" s="3" t="s">
         <v>22</v>
@@ -11887,7 +11879,7 @@
         <v>1</v>
       </c>
       <c r="K214" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L214" s="3" t="s">
         <v>10</v>
@@ -11896,15 +11888,15 @@
         <v>86</v>
       </c>
       <c r="N214" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B215" s="20" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C215" s="3" t="s">
         <v>22</v>
@@ -11933,7 +11925,7 @@
         <v>30.299999999999997</v>
       </c>
       <c r="K215" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L215" s="3" t="s">
         <v>10</v>
@@ -11942,15 +11934,15 @@
         <v>86</v>
       </c>
       <c r="N215" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B216" s="20" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>22</v>
@@ -11979,7 +11971,7 @@
         <v>16.799999999999997</v>
       </c>
       <c r="K216" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L216" s="3" t="s">
         <v>10</v>
@@ -11988,15 +11980,15 @@
         <v>86</v>
       </c>
       <c r="N216" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B217" s="20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C217" s="3" t="s">
         <v>22</v>
@@ -12025,7 +12017,7 @@
         <v>14.100000000000001</v>
       </c>
       <c r="K217" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L217" s="3" t="s">
         <v>10</v>
@@ -12034,15 +12026,15 @@
         <v>86</v>
       </c>
       <c r="N217" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B218" s="19" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C218" s="3" t="s">
         <v>22</v>
@@ -12071,7 +12063,7 @@
         <v>43.2</v>
       </c>
       <c r="K218" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L218" s="3" t="s">
         <v>10</v>
@@ -12080,15 +12072,15 @@
         <v>86</v>
       </c>
       <c r="N218" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B219" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C219" s="3" t="s">
         <v>22</v>
@@ -12117,7 +12109,7 @@
         <v>24.200000000000003</v>
       </c>
       <c r="K219" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L219" s="3" t="s">
         <v>10</v>
@@ -12126,15 +12118,15 @@
         <v>86</v>
       </c>
       <c r="N219" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B220" s="19" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C220" s="3" t="s">
         <v>22</v>
@@ -12163,7 +12155,7 @@
         <v>15.400000000000006</v>
       </c>
       <c r="K220" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L220" s="3" t="s">
         <v>10</v>
@@ -12172,15 +12164,15 @@
         <v>86</v>
       </c>
       <c r="N220" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A221" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B221" s="19" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C221" s="3" t="s">
         <v>22</v>
@@ -12209,7 +12201,7 @@
         <v>7.7000000000000028</v>
       </c>
       <c r="K221" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L221" s="3" t="s">
         <v>10</v>
@@ -12218,15 +12210,15 @@
         <v>86</v>
       </c>
       <c r="N221" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A222" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B222" s="19" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C222" s="3" t="s">
         <v>22</v>
@@ -12255,7 +12247,7 @@
         <v>13</v>
       </c>
       <c r="K222" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L222" s="3" t="s">
         <v>10</v>
@@ -12264,15 +12256,15 @@
         <v>86</v>
       </c>
       <c r="N222" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="223" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B223" s="23" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C223" s="3" t="s">
         <v>22</v>
@@ -12301,7 +12293,7 @@
         <v>17.200000000000003</v>
       </c>
       <c r="K223" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L223" s="3" t="s">
         <v>10</v>
@@ -12310,15 +12302,15 @@
         <v>86</v>
       </c>
       <c r="N223" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A224" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B224" s="19" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C224" s="3" t="s">
         <v>22</v>
@@ -12347,7 +12339,7 @@
         <v>7.7999999999999972</v>
       </c>
       <c r="K224" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L224" s="3" t="s">
         <v>10</v>
@@ -12356,15 +12348,15 @@
         <v>86</v>
       </c>
       <c r="N224" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B225" s="19" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C225" s="3" t="s">
         <v>22</v>
@@ -12393,7 +12385,7 @@
         <v>14.400000000000006</v>
       </c>
       <c r="K225" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L225" s="3" t="s">
         <v>10</v>
@@ -12402,15 +12394,15 @@
         <v>86</v>
       </c>
       <c r="N225" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B226" s="19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>22</v>
@@ -12439,7 +12431,7 @@
         <v>23.5</v>
       </c>
       <c r="K226" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L226" s="3" t="s">
         <v>10</v>
@@ -12448,15 +12440,15 @@
         <v>86</v>
       </c>
       <c r="N226" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B227" s="19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C227" s="3" t="s">
         <v>22</v>
@@ -12485,7 +12477,7 @@
         <v>4</v>
       </c>
       <c r="K227" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L227" s="3" t="s">
         <v>10</v>
@@ -12494,15 +12486,15 @@
         <v>86</v>
       </c>
       <c r="N227" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B228" s="19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C228" s="3" t="s">
         <v>22</v>
@@ -12531,7 +12523,7 @@
         <v>10.599999999999994</v>
       </c>
       <c r="K228" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L228" s="3" t="s">
         <v>10</v>
@@ -12540,15 +12532,15 @@
         <v>86</v>
       </c>
       <c r="N228" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B229" s="19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C229" s="3" t="s">
         <v>22</v>
@@ -12577,7 +12569,7 @@
         <v>7</v>
       </c>
       <c r="K229" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L229" s="3" t="s">
         <v>10</v>
@@ -12586,15 +12578,15 @@
         <v>86</v>
       </c>
       <c r="N229" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B230" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>22</v>
@@ -12623,7 +12615,7 @@
         <v>6</v>
       </c>
       <c r="K230" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L230" s="3" t="s">
         <v>10</v>
@@ -12632,15 +12624,15 @@
         <v>86</v>
       </c>
       <c r="N230" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B231" s="19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C231" s="3" t="s">
         <v>22</v>
@@ -12669,7 +12661,7 @@
         <v>6</v>
       </c>
       <c r="K231" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L231" s="3" t="s">
         <v>10</v>
@@ -12678,15 +12670,15 @@
         <v>86</v>
       </c>
       <c r="N231" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B232" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C232" s="3" t="s">
         <v>22</v>
@@ -12715,7 +12707,7 @@
         <v>13.200000000000003</v>
       </c>
       <c r="K232" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L232" s="3" t="s">
         <v>10</v>
@@ -12724,15 +12716,15 @@
         <v>86</v>
       </c>
       <c r="N232" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B233" s="19" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C233" s="3" t="s">
         <v>22</v>
@@ -12761,7 +12753,7 @@
         <v>5.5</v>
       </c>
       <c r="K233" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L233" s="3" t="s">
         <v>10</v>
@@ -12770,15 +12762,15 @@
         <v>86</v>
       </c>
       <c r="N233" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B234" s="19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C234" s="3" t="s">
         <v>22</v>
@@ -12807,7 +12799,7 @@
         <v>58.2</v>
       </c>
       <c r="K234" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L234" s="3" t="s">
         <v>10</v>
@@ -12816,15 +12808,15 @@
         <v>86</v>
       </c>
       <c r="N234" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B235" s="24" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C235" s="3" t="s">
         <v>22</v>
@@ -12851,7 +12843,7 @@
         <v>12</v>
       </c>
       <c r="K235" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L235" s="3" t="s">
         <v>10</v>
@@ -12860,15 +12852,15 @@
         <v>86</v>
       </c>
       <c r="N235" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B236" s="24" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C236" s="3" t="s">
         <v>22</v>
@@ -12895,7 +12887,7 @@
         <v>12</v>
       </c>
       <c r="K236" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L236" s="3" t="s">
         <v>10</v>
@@ -12904,15 +12896,15 @@
         <v>86</v>
       </c>
       <c r="N236" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B237" s="24" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C237" s="3" t="s">
         <v>22</v>
@@ -12939,7 +12931,7 @@
         <v>12</v>
       </c>
       <c r="K237" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L237" s="3" t="s">
         <v>10</v>
@@ -12948,15 +12940,15 @@
         <v>86</v>
       </c>
       <c r="N237" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B238" s="24" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>22</v>
@@ -12983,7 +12975,7 @@
         <v>12</v>
       </c>
       <c r="K238" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L238" s="3" t="s">
         <v>10</v>
@@ -12992,15 +12984,15 @@
         <v>86</v>
       </c>
       <c r="N238" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B239" s="24" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C239" s="3" t="s">
         <v>22</v>
@@ -13027,7 +13019,7 @@
         <v>12</v>
       </c>
       <c r="K239" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L239" s="3" t="s">
         <v>10</v>
@@ -13036,15 +13028,15 @@
         <v>86</v>
       </c>
       <c r="N239" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B240" s="24" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>22</v>
@@ -13071,7 +13063,7 @@
         <v>12</v>
       </c>
       <c r="K240" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L240" s="3" t="s">
         <v>10</v>
@@ -13080,15 +13072,15 @@
         <v>86</v>
       </c>
       <c r="N240" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B241" s="24" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C241" s="3" t="s">
         <v>22</v>
@@ -13115,7 +13107,7 @@
         <v>12</v>
       </c>
       <c r="K241" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L241" s="3" t="s">
         <v>10</v>
@@ -13124,15 +13116,15 @@
         <v>86</v>
       </c>
       <c r="N241" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B242" s="24" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C242" s="3" t="s">
         <v>22</v>
@@ -13159,7 +13151,7 @@
         <v>12</v>
       </c>
       <c r="K242" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L242" s="3" t="s">
         <v>10</v>
@@ -13168,15 +13160,15 @@
         <v>86</v>
       </c>
       <c r="N242" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B243" s="24" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C243" s="3" t="s">
         <v>22</v>
@@ -13203,7 +13195,7 @@
         <v>12</v>
       </c>
       <c r="K243" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L243" s="3" t="s">
         <v>10</v>
@@ -13212,15 +13204,15 @@
         <v>86</v>
       </c>
       <c r="N243" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A244" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B244" s="24" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C244" s="3" t="s">
         <v>22</v>
@@ -13247,7 +13239,7 @@
         <v>12</v>
       </c>
       <c r="K244" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L244" s="3" t="s">
         <v>10</v>
@@ -13256,15 +13248,15 @@
         <v>86</v>
       </c>
       <c r="N244" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B245" s="24" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C245" s="3" t="s">
         <v>22</v>
@@ -13291,7 +13283,7 @@
         <v>12</v>
       </c>
       <c r="K245" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L245" s="3" t="s">
         <v>10</v>
@@ -13300,15 +13292,15 @@
         <v>86</v>
       </c>
       <c r="N245" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B246" s="24" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>22</v>
@@ -13335,7 +13327,7 @@
         <v>12</v>
       </c>
       <c r="K246" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L246" s="3" t="s">
         <v>10</v>
@@ -13344,15 +13336,15 @@
         <v>86</v>
       </c>
       <c r="N246" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B247" s="24" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>22</v>
@@ -13379,7 +13371,7 @@
         <v>12</v>
       </c>
       <c r="K247" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L247" s="3" t="s">
         <v>10</v>
@@ -13388,15 +13380,15 @@
         <v>86</v>
       </c>
       <c r="N247" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A248" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B248" s="24" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>22</v>
@@ -13423,7 +13415,7 @@
         <v>12</v>
       </c>
       <c r="K248" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L248" s="3" t="s">
         <v>10</v>
@@ -13432,15 +13424,15 @@
         <v>86</v>
       </c>
       <c r="N248" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B249" s="24" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C249" s="3" t="s">
         <v>22</v>
@@ -13467,7 +13459,7 @@
         <v>12</v>
       </c>
       <c r="K249" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L249" s="3" t="s">
         <v>10</v>
@@ -13476,15 +13468,15 @@
         <v>86</v>
       </c>
       <c r="N249" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A250" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B250" s="24" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>22</v>
@@ -13511,7 +13503,7 @@
         <v>12</v>
       </c>
       <c r="K250" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L250" s="3" t="s">
         <v>10</v>
@@ -13520,15 +13512,15 @@
         <v>86</v>
       </c>
       <c r="N250" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B251" s="24" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C251" s="3" t="s">
         <v>22</v>
@@ -13555,7 +13547,7 @@
         <v>12</v>
       </c>
       <c r="K251" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L251" s="3" t="s">
         <v>10</v>
@@ -13564,15 +13556,15 @@
         <v>86</v>
       </c>
       <c r="N251" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B252" s="24" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C252" s="3" t="s">
         <v>22</v>
@@ -13599,7 +13591,7 @@
         <v>12</v>
       </c>
       <c r="K252" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L252" s="3" t="s">
         <v>10</v>
@@ -13608,15 +13600,15 @@
         <v>86</v>
       </c>
       <c r="N252" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B253" s="24" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C253" s="3" t="s">
         <v>22</v>
@@ -13643,7 +13635,7 @@
         <v>12</v>
       </c>
       <c r="K253" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L253" s="3" t="s">
         <v>10</v>
@@ -13652,15 +13644,15 @@
         <v>86</v>
       </c>
       <c r="N253" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A254" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B254" s="24" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C254" s="3" t="s">
         <v>22</v>
@@ -13687,7 +13679,7 @@
         <v>12</v>
       </c>
       <c r="K254" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L254" s="3" t="s">
         <v>10</v>
@@ -13696,15 +13688,15 @@
         <v>86</v>
       </c>
       <c r="N254" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B255" s="24" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C255" s="3" t="s">
         <v>22</v>
@@ -13731,7 +13723,7 @@
         <v>12</v>
       </c>
       <c r="K255" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L255" s="3" t="s">
         <v>10</v>
@@ -13740,15 +13732,15 @@
         <v>86</v>
       </c>
       <c r="N255" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B256" s="24" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C256" s="3" t="s">
         <v>22</v>
@@ -13775,7 +13767,7 @@
         <v>12</v>
       </c>
       <c r="K256" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L256" s="3" t="s">
         <v>10</v>
@@ -13784,15 +13776,15 @@
         <v>86</v>
       </c>
       <c r="N256" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B257" s="24" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C257" s="3" t="s">
         <v>22</v>
@@ -13819,7 +13811,7 @@
         <v>12</v>
       </c>
       <c r="K257" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L257" s="3" t="s">
         <v>10</v>
@@ -13828,15 +13820,15 @@
         <v>86</v>
       </c>
       <c r="N257" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B258" s="24" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C258" s="3" t="s">
         <v>22</v>
@@ -13863,7 +13855,7 @@
         <v>12</v>
       </c>
       <c r="K258" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L258" s="3" t="s">
         <v>10</v>
@@ -13872,15 +13864,15 @@
         <v>86</v>
       </c>
       <c r="N258" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B259" s="24" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C259" s="3" t="s">
         <v>22</v>
@@ -13907,7 +13899,7 @@
         <v>12</v>
       </c>
       <c r="K259" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L259" s="3" t="s">
         <v>10</v>
@@ -13916,15 +13908,15 @@
         <v>86</v>
       </c>
       <c r="N259" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B260" s="24" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C260" s="3" t="s">
         <v>22</v>
@@ -13951,7 +13943,7 @@
         <v>12</v>
       </c>
       <c r="K260" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L260" s="3" t="s">
         <v>10</v>
@@ -13960,15 +13952,15 @@
         <v>86</v>
       </c>
       <c r="N260" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B261" s="24" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C261" s="3" t="s">
         <v>22</v>
@@ -13995,7 +13987,7 @@
         <v>12</v>
       </c>
       <c r="K261" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L261" s="3" t="s">
         <v>10</v>
@@ -14004,15 +13996,15 @@
         <v>86</v>
       </c>
       <c r="N261" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A262" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B262" s="24" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C262" s="3" t="s">
         <v>22</v>
@@ -14039,7 +14031,7 @@
         <v>12</v>
       </c>
       <c r="K262" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L262" s="3" t="s">
         <v>10</v>
@@ -14048,15 +14040,15 @@
         <v>86</v>
       </c>
       <c r="N262" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B263" s="24" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C263" s="3" t="s">
         <v>22</v>
@@ -14083,7 +14075,7 @@
         <v>12</v>
       </c>
       <c r="K263" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L263" s="3" t="s">
         <v>10</v>
@@ -14092,15 +14084,15 @@
         <v>86</v>
       </c>
       <c r="N263" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B264" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C264" s="3" t="s">
         <v>22</v>
@@ -14127,7 +14119,7 @@
         <v>12</v>
       </c>
       <c r="K264" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L264" s="3" t="s">
         <v>10</v>
@@ -14136,15 +14128,15 @@
         <v>86</v>
       </c>
       <c r="N264" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B265" s="24" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C265" s="3" t="s">
         <v>22</v>
@@ -14171,7 +14163,7 @@
         <v>12</v>
       </c>
       <c r="K265" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L265" s="3" t="s">
         <v>10</v>
@@ -14180,18 +14172,18 @@
         <v>86</v>
       </c>
       <c r="N265" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B266" s="24" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D266" s="25">
         <v>79.919178000000002</v>
@@ -14210,13 +14202,13 @@
         <v>0.29000000000000004</v>
       </c>
       <c r="I266" s="22" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="J266" s="5">
         <v>0.71</v>
       </c>
       <c r="K266" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L266" s="3" t="s">
         <v>10</v>
@@ -14225,18 +14217,18 @@
         <v>16</v>
       </c>
       <c r="N266" s="6" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B267" s="24" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D267" s="25">
         <v>79.875488000000004</v>
@@ -14255,33 +14247,33 @@
         <v>0.29000000000000004</v>
       </c>
       <c r="I267" s="22" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="J267" s="5">
         <v>1.71</v>
       </c>
       <c r="K267" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L267" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M267" s="3" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="N267" s="6" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A268" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="B268" s="24" t="s">
         <v>495</v>
       </c>
-      <c r="B268" s="24" t="s">
-        <v>501</v>
-      </c>
       <c r="C268" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D268" s="25">
         <v>79.718778</v>
@@ -14300,13 +14292,13 @@
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="I268" s="22" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="J268" s="5">
         <v>0.9</v>
       </c>
       <c r="K268" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L268" s="3" t="s">
         <v>10</v>
@@ -14315,15 +14307,15 @@
         <v>16</v>
       </c>
       <c r="N268" s="6" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A269" s="4" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C269" s="3" t="s">
         <v>25</v>
@@ -14351,24 +14343,24 @@
         <v>0</v>
       </c>
       <c r="K269" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L269" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="M269" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="N269" s="6" t="s">
         <v>379</v>
-      </c>
-      <c r="N269" s="6" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A270" s="4" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C270" s="3" t="s">
         <v>25</v>
@@ -14396,27 +14388,27 @@
         <v>0</v>
       </c>
       <c r="K270" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L270" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="M270" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="N270" s="6" t="s">
         <v>379</v>
-      </c>
-      <c r="N270" s="6" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B271" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C271" s="3" t="s">
         <v>382</v>
-      </c>
-      <c r="C271" s="3" t="s">
-        <v>383</v>
       </c>
       <c r="D271" s="5">
         <v>1.2865660000000001</v>
@@ -14435,13 +14427,13 @@
         <v>1.5</v>
       </c>
       <c r="I271" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J271" s="5">
         <v>6.5</v>
       </c>
       <c r="K271" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L271" s="3" t="s">
         <v>23</v>
@@ -14450,18 +14442,18 @@
         <v>86</v>
       </c>
       <c r="N271" s="33" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A272" s="4" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D272" s="8">
         <v>1.2669999999999999</v>
@@ -14480,13 +14472,13 @@
         <v>1</v>
       </c>
       <c r="I272" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J272" s="5">
         <v>0</v>
       </c>
       <c r="K272" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L272" s="3" t="s">
         <v>23</v>
@@ -14495,18 +14487,18 @@
         <v>86</v>
       </c>
       <c r="N272" s="33" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
     </row>
     <row r="273" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D273" s="8">
         <v>1.4670000000000001</v>
@@ -14525,7 +14517,7 @@
         <v>8.9999999999999969E-2</v>
       </c>
       <c r="I273" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J273" s="5">
         <v>0.91</v>
@@ -14540,7 +14532,7 @@
         <v>16</v>
       </c>
       <c r="N273" s="33" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
     </row>
     <row r="274" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
